--- a/diseases/d023/2010-2014.xlsx
+++ b/diseases/d023/2010-2014.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2197,9 +2191,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2780,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3381,9 +3369,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3973,9 +3958,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4565,9 +4547,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5157,9 +5136,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5749,9 +5725,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6341,9 +6314,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6933,9 +6903,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7525,9 +7492,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8117,9 +8081,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8709,9 +8670,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9105,9 +9063,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9697,9 +9652,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10289,9 +10241,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10881,9 +10830,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11473,9 +11419,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -12065,9 +12008,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12657,9 +12597,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13249,9 +13186,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13841,9 +13775,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14433,9 +14364,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -15025,9 +14953,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15617,9 +15542,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -16209,9 +16131,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -16605,9 +16524,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -17197,9 +17113,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -17789,9 +17702,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18381,9 +18291,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -18973,9 +18880,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -19565,9 +19469,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -20157,9 +20058,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -20749,9 +20647,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -21341,9 +21236,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -22377,9 +22269,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -23561,9 +23450,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -24893,9 +24779,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -26077,9 +25960,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -26473,9 +26353,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -27805,9 +27682,6 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
@@ -28989,9 +28863,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -30173,9 +30044,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -31357,9 +31225,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -32689,9 +32554,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -33873,9 +33735,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -35057,9 +34916,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -36389,9 +36245,6 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -37573,9 +37426,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -38905,9 +38755,6 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0</v>
       </c>
@@ -40089,9 +39936,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -41273,9 +41117,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -41669,9 +41510,6 @@
       <c r="O275" t="n">
         <v>0</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0</v>
       </c>
@@ -43001,9 +42839,6 @@
       <c r="O284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
@@ -44185,9 +44020,6 @@
       <c r="O292" t="n">
         <v>0</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0</v>
       </c>
@@ -45369,9 +45201,6 @@
       <c r="O300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0</v>
       </c>
@@ -46553,9 +46382,6 @@
       <c r="O308" t="n">
         <v>0</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0</v>
       </c>
@@ -47885,9 +47711,6 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -49069,9 +48892,6 @@
       <c r="O325" t="n">
         <v>0</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0</v>
       </c>
@@ -50401,9 +50221,6 @@
       <c r="O334" t="n">
         <v>0</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0</v>
       </c>
@@ -51585,9 +51402,6 @@
       <c r="O342" t="n">
         <v>0</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0</v>
       </c>
@@ -52769,9 +52583,6 @@
       <c r="O350" t="n">
         <v>0</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>0</v>
       </c>
@@ -54101,9 +53912,6 @@
       <c r="O359" t="n">
         <v>0</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>0</v>
       </c>
@@ -55283,9 +55091,6 @@
         <v>0</v>
       </c>
       <c r="O367" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q367" t="n">
         <v>0</v>
       </c>
       <c r="R367" t="n">
